--- a/public/assets/ICF Workshop.xlsx
+++ b/public/assets/ICF Workshop.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\amaltas-university-latest\amaltas-university\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4EA46B-364E-4E00-90BC-566992448E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C27B8A-5DF4-4618-9428-78D2A0E8186B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="388">
   <si>
     <t>Timestamp</t>
   </si>
@@ -790,6 +790,9 @@
     <t>‪98262 47595‬</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>puneet1984@gmail.com</t>
   </si>
   <si>
@@ -1172,64 +1175,39 @@
   </si>
   <si>
     <t>Dr. Aman</t>
+  </si>
+  <si>
+    <t>Dr. Mahesh Kumar Jain</t>
+  </si>
+  <si>
+    <t>vijaychlcbcc@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Vijay Bairagi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF434343"/>
-      <name val="Roboto"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5B3F86"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8F9FA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="23">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1237,441 +1215,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF5B3F86"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF442F65"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF5B3F86"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF442F65"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF442F65"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF442F65"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF442F65"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF442F65"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1694,44 +1249,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1761,12 +1316,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1805,2118 +1360,2171 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="147.7109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12">
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>46252.694108796299</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2">
         <v>9300409555</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>46255.475023148138</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3">
         <v>9755636785</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>46255.476666666669</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4">
         <v>9650956946</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>46255.505543981482</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5">
         <v>8174848145</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>46255.507199074083</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6">
         <v>7879388387</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>46255.510648148149</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7">
         <v>9039995515</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>46255.510937500003</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8">
         <v>9561138588</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>46255.510949074072</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9">
         <v>8827665607</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>46255.511736111112</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10">
         <v>8494996954</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>46255.512418981481</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11">
         <v>6265569385</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>46255.512916666667</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12">
         <v>9907262765</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>46255.514189814807</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13">
         <v>7389626282</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>46255.515092592592</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14">
         <v>8983933684</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>46255.545069444437</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15">
         <v>8482840108</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>46255.556342592587</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16">
         <v>7895135250</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" t="s">
         <v>66</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>46255.569016203714</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17">
         <v>7822911210</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" t="s">
         <v>67</v>
       </c>
-      <c r="H17" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>46255.583124999997</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18">
         <v>9358202887</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" t="s">
         <v>71</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>46255.601620370369</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19">
         <v>9826247595</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" t="s">
         <v>75</v>
       </c>
-      <c r="H19" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>46255.715567129628</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20">
         <v>9039923684</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" t="s">
         <v>79</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+      <c r="H20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>46255.716550925928</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21">
         <v>8887504512</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
+      <c r="H21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>46255.758125</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22">
         <v>9981964722</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" t="s">
         <v>88</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
+      <c r="H22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>46256.371238425927</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23">
         <v>9027495721</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" t="s">
         <v>89</v>
       </c>
-      <c r="H23" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>46256.462129629632</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24">
         <v>9826781805</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" t="s">
         <v>92</v>
       </c>
-      <c r="H24" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
+      <c r="H24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>46258.460543981477</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" t="s">
         <v>25</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25">
         <v>7415777514</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" t="s">
         <v>95</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+      <c r="H25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>46258.629189814812</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" t="s">
         <v>98</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" t="s">
         <v>100</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26">
         <v>7000633830</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" t="s">
         <v>97</v>
       </c>
-      <c r="H26" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
+      <c r="H26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>46258.635474537034</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" t="s">
         <v>102</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" t="s">
         <v>104</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27">
         <v>6266062087</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" t="s">
         <v>101</v>
       </c>
-      <c r="H27" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
+      <c r="H27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>46258.657175925917</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28">
         <v>8435700099</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" t="s">
         <v>105</v>
       </c>
-      <c r="H28" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
+      <c r="H28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>46258.657407407409</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" t="s">
         <v>107</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" t="s">
         <v>108</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" t="s">
         <v>104</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29">
         <v>6263274181</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" t="s">
         <v>107</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
+      <c r="H29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>46258.657812500001</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" t="s">
         <v>110</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" t="s">
         <v>111</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" t="s">
         <v>112</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" t="s">
         <v>100</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30">
         <v>7725050044</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" t="s">
         <v>110</v>
       </c>
-      <c r="H30" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
+      <c r="H30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>46258.666689814818</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" t="s">
         <v>113</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" t="s">
         <v>100</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31">
         <v>7724081964</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" t="s">
         <v>113</v>
       </c>
-      <c r="H31" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
+      <c r="H31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>46258.680208333331</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" t="s">
         <v>39</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32">
         <v>8269290802</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" t="s">
         <v>115</v>
       </c>
-      <c r="H32" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
+      <c r="H32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>46260.799618055556</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" t="s">
         <v>117</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" t="s">
         <v>120</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33">
         <v>8878377821</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" t="s">
         <v>117</v>
       </c>
-      <c r="H33" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
+      <c r="H33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>46260.972731481481</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" t="s">
         <v>121</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" t="s">
         <v>122</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" t="s">
         <v>123</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" t="s">
         <v>124</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34">
         <v>7415354534</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" t="s">
         <v>121</v>
       </c>
-      <c r="H34" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8">
+      <c r="H34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>46261.376689814817</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" t="s">
         <v>125</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" t="s">
         <v>35</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35">
         <v>7988860585</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" t="s">
         <v>125</v>
       </c>
-      <c r="H35" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
+      <c r="H35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>46261.445763888893</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" t="s">
         <v>128</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" t="s">
         <v>129</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" t="s">
         <v>130</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" t="s">
         <v>131</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36">
         <v>9555152991</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" t="s">
         <v>128</v>
       </c>
-      <c r="H36" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8">
+      <c r="H36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>46263.532326388893</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" t="s">
         <v>132</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" t="s">
         <v>133</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" t="s">
         <v>51</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37">
         <v>7507594401</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" t="s">
         <v>132</v>
       </c>
-      <c r="H37" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4">
+      <c r="H37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>46263.532361111109</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" t="s">
         <v>134</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" t="s">
         <v>135</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" t="s">
         <v>73</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38">
         <v>8871449662</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" t="s">
         <v>134</v>
       </c>
-      <c r="H38" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="8">
+      <c r="H38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39">
         <v>46263.53329861111</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" t="s">
         <v>123</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39">
         <v>9811620075</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" t="s">
         <v>136</v>
       </c>
-      <c r="H39" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+      <c r="H39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>46263.534525462957</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" t="s">
         <v>138</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" t="s">
         <v>139</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" t="s">
         <v>73</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" t="s">
         <v>140</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40">
         <v>7580938634</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" t="s">
         <v>138</v>
       </c>
-      <c r="H40" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="8">
+      <c r="H40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>46263.535405092603</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" t="s">
         <v>141</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" t="s">
         <v>142</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" t="s">
         <v>143</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" t="s">
         <v>144</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41">
         <v>8871751824</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" t="s">
         <v>141</v>
       </c>
-      <c r="H41" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
+      <c r="H41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>46263.53564814815</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" t="s">
         <v>146</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" t="s">
         <v>58</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" t="s">
         <v>35</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42">
         <v>7000771505</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" t="s">
         <v>145</v>
       </c>
-      <c r="H42" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="8">
+      <c r="H42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>46263.535844907397</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" t="s">
         <v>147</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" t="s">
         <v>148</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" t="s">
         <v>149</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" t="s">
         <v>144</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43">
         <v>8989574245</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G43" t="s">
         <v>147</v>
       </c>
-      <c r="H43" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4">
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>46263.536226851851</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" t="s">
         <v>150</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" t="s">
         <v>151</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" t="s">
         <v>152</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" t="s">
         <v>153</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44">
         <v>9685006677</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" t="s">
         <v>150</v>
       </c>
-      <c r="H44" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="8">
+      <c r="H44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>46263.538194444453</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" t="s">
         <v>154</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" t="s">
         <v>155</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" t="s">
         <v>73</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" t="s">
         <v>156</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45">
         <v>9630929030</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G45" t="s">
         <v>154</v>
       </c>
-      <c r="H45" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="4">
+      <c r="H45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>46263.539305555547</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" t="s">
         <v>157</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" t="s">
         <v>158</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" t="s">
         <v>159</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" t="s">
         <v>160</v>
       </c>
-      <c r="F46" s="6">
+      <c r="F46">
         <v>6387573650</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" t="s">
         <v>157</v>
       </c>
-      <c r="H46" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="8">
+      <c r="H46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47">
         <v>46263.539988425917</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" t="s">
         <v>161</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" t="s">
         <v>162</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" t="s">
         <v>47</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" t="s">
         <v>163</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47">
         <v>7987868218</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" t="s">
         <v>161</v>
       </c>
-      <c r="H47" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
+      <c r="H47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48">
         <v>46263.541504629633</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" t="s">
         <v>164</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" t="s">
         <v>165</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" t="s">
         <v>73</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" t="s">
         <v>166</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48">
         <v>6287275934</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G48" t="s">
         <v>167</v>
       </c>
-      <c r="H48" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="8">
+      <c r="H48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49">
         <v>46263.541817129633</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" t="s">
         <v>168</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" t="s">
         <v>169</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" t="s">
         <v>83</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49">
         <v>9713935458</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G49" t="s">
         <v>168</v>
       </c>
-      <c r="H49" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
+      <c r="H49" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50">
         <v>46263.544178240743</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" t="s">
         <v>170</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" t="s">
         <v>171</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" t="s">
         <v>172</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" t="s">
         <v>25</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50">
         <v>9424419559</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="G50" t="s">
         <v>170</v>
       </c>
-      <c r="H50" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="8">
+      <c r="H50" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51">
         <v>46263.545567129629</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" t="s">
         <v>173</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" t="s">
         <v>174</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" t="s">
         <v>51</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" t="s">
         <v>25</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51">
         <v>8570018061</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" t="s">
         <v>175</v>
       </c>
-      <c r="H51" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
+      <c r="H51" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52">
         <v>46263.548356481479</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" t="s">
         <v>176</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" t="s">
         <v>177</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" t="s">
         <v>178</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" t="s">
         <v>179</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52">
         <v>9424013131</v>
       </c>
-      <c r="G52" s="5" t="s">
+      <c r="G52" t="s">
         <v>176</v>
       </c>
-      <c r="H52" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="8">
+      <c r="H52" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53">
         <v>46263.550671296303</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" t="s">
         <v>180</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" t="s">
         <v>181</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" t="s">
         <v>182</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" t="s">
         <v>160</v>
       </c>
-      <c r="F53" s="10">
+      <c r="F53">
         <v>9068625767</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" t="s">
         <v>180</v>
       </c>
-      <c r="H53" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4">
+      <c r="H53" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54">
         <v>46263.558761574073</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" t="s">
         <v>183</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" t="s">
         <v>184</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D54" t="s">
         <v>185</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" t="s">
         <v>153</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54">
         <v>9981045771</v>
       </c>
-      <c r="G54" s="5" t="s">
+      <c r="G54" t="s">
         <v>183</v>
       </c>
-      <c r="H54" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="8">
+      <c r="H54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55">
         <v>46263.560706018521</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" t="s">
         <v>186</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" t="s">
         <v>187</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" t="s">
         <v>83</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" t="s">
         <v>188</v>
       </c>
-      <c r="F55" s="10">
+      <c r="F55">
         <v>9421613563</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" t="s">
         <v>186</v>
       </c>
-      <c r="H55" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="4">
+      <c r="H55" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56">
         <v>46263.564583333333</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" t="s">
         <v>189</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" t="s">
         <v>190</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" t="s">
         <v>24</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" t="s">
         <v>124</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56">
         <v>9328809898</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G56" t="s">
         <v>189</v>
       </c>
-      <c r="H56" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="8">
+      <c r="H56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57">
         <v>46263.573020833333</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" t="s">
         <v>191</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" t="s">
         <v>192</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" t="s">
         <v>24</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="10">
+      <c r="F57">
         <v>9752738138</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" t="s">
         <v>191</v>
       </c>
-      <c r="H57" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4">
+      <c r="H57" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58">
         <v>46263.576574074083</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" t="s">
         <v>193</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" t="s">
         <v>194</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" t="s">
         <v>123</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" t="s">
         <v>195</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58">
         <v>7772836095</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" t="s">
         <v>193</v>
       </c>
-      <c r="H58" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="8">
+      <c r="H58" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59">
         <v>46263.578310185178</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" t="s">
         <v>196</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" t="s">
         <v>197</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" t="s">
         <v>198</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" t="s">
         <v>195</v>
       </c>
-      <c r="F59" s="10">
+      <c r="F59">
         <v>9893996106</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="G59" t="s">
         <v>196</v>
       </c>
-      <c r="H59" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="4">
+      <c r="H59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60">
         <v>46263.593414351853</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" t="s">
         <v>199</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" t="s">
         <v>200</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" t="s">
         <v>73</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" t="s">
         <v>163</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F60">
         <v>9109110092</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="G60" t="s">
         <v>201</v>
       </c>
-      <c r="H60" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="8">
+      <c r="H60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61">
         <v>46263.749513888892</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" t="s">
         <v>202</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" t="s">
         <v>203</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" t="s">
         <v>123</v>
       </c>
-      <c r="E61" s="9" t="s">
+      <c r="E61" t="s">
         <v>204</v>
       </c>
-      <c r="F61" s="10">
+      <c r="F61">
         <v>9407133385</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="G61" t="s">
         <v>202</v>
       </c>
-      <c r="H61" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="4">
+      <c r="H61" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62">
         <v>46265.339282407411</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" t="s">
         <v>205</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" t="s">
         <v>206</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D62" t="s">
         <v>207</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" t="s">
         <v>208</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F62">
         <v>7771075573</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" t="s">
         <v>205</v>
       </c>
-      <c r="H62" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="8">
+      <c r="H62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63">
         <v>46265.34171296296</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" t="s">
         <v>209</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" t="s">
         <v>210</v>
       </c>
-      <c r="D63" s="9" t="s">
+      <c r="D63" t="s">
         <v>211</v>
       </c>
-      <c r="E63" s="9" t="s">
+      <c r="E63" t="s">
         <v>140</v>
       </c>
-      <c r="F63" s="10">
+      <c r="F63">
         <v>8441905981</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="G63" t="s">
         <v>209</v>
       </c>
-      <c r="H63" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4">
+      <c r="H63" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64">
         <v>46265.612719907411</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" t="s">
         <v>212</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" t="s">
         <v>213</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" t="s">
         <v>214</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" t="s">
         <v>215</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64">
         <v>9826647786</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="G64" t="s">
         <v>212</v>
       </c>
-      <c r="H64" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="8">
+      <c r="H64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65">
         <v>46266.355821759258</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" t="s">
         <v>216</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" t="s">
         <v>217</v>
       </c>
-      <c r="D65" s="9" t="s">
+      <c r="D65" t="s">
         <v>218</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="E65" t="s">
         <v>219</v>
       </c>
-      <c r="F65" s="10">
+      <c r="F65">
         <v>9425049415</v>
       </c>
-      <c r="G65" s="9" t="s">
+      <c r="G65" t="s">
         <v>216</v>
       </c>
-      <c r="H65" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="4">
+      <c r="H65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66">
         <v>46266.376076388893</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" t="s">
         <v>220</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" t="s">
         <v>221</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D66" t="s">
         <v>222</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" t="s">
         <v>140</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66">
         <v>7742627345</v>
       </c>
-      <c r="G66" s="5" t="s">
+      <c r="G66" t="s">
         <v>220</v>
       </c>
-      <c r="H66" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="16">
+      <c r="H66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67">
         <v>46266.376111111109</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" t="s">
         <v>223</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" t="s">
         <v>224</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" t="s">
         <v>73</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" t="s">
         <v>140</v>
       </c>
-      <c r="F67" s="18">
+      <c r="F67">
         <v>7266935975</v>
       </c>
-      <c r="G67" s="17" t="s">
+      <c r="G67" t="s">
         <v>223</v>
       </c>
-      <c r="H67" s="19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="20">
+      <c r="H67" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68">
         <v>46266.515208333331</v>
       </c>
-      <c r="B68" s="21" t="s">
+      <c r="B68" t="s">
         <v>225</v>
       </c>
-      <c r="C68" s="21" t="s">
+      <c r="C68" t="s">
         <v>226</v>
       </c>
-      <c r="D68" s="21" t="s">
+      <c r="D68" t="s">
         <v>227</v>
       </c>
-      <c r="E68" s="21" t="s">
+      <c r="E68" t="s">
         <v>228</v>
       </c>
-      <c r="F68" s="22">
+      <c r="F68">
         <v>7024471185</v>
       </c>
-      <c r="G68" s="21" t="s">
+      <c r="G68" t="s">
         <v>225</v>
       </c>
-      <c r="H68" s="23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="24">
+      <c r="H68" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69">
         <v>46266.723414351851</v>
       </c>
-      <c r="B69" s="25" t="s">
+      <c r="B69" t="s">
         <v>229</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" t="s">
         <v>230</v>
       </c>
-      <c r="D69" s="25" t="s">
+      <c r="D69" t="s">
         <v>231</v>
       </c>
-      <c r="E69" s="25" t="s">
+      <c r="E69" t="s">
         <v>232</v>
       </c>
-      <c r="F69" s="26">
+      <c r="F69">
         <v>8839400836</v>
       </c>
-      <c r="G69" s="25" t="s">
+      <c r="G69" t="s">
         <v>229</v>
       </c>
-      <c r="H69" s="27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="4">
+      <c r="H69" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70">
         <v>46266.726030092592</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" t="s">
         <v>233</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" t="s">
         <v>234</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" t="s">
         <v>235</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E70" t="s">
         <v>236</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70">
         <v>9926841097</v>
       </c>
-      <c r="G70" s="5" t="s">
+      <c r="G70" t="s">
         <v>233</v>
       </c>
-      <c r="H70" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="8">
+      <c r="H70" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71">
         <v>46266.784849537027</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" t="s">
         <v>237</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" t="s">
         <v>238</v>
       </c>
-      <c r="D71" s="9" t="s">
+      <c r="D71" t="s">
         <v>239</v>
       </c>
-      <c r="E71" s="9" t="s">
+      <c r="E71" t="s">
         <v>240</v>
       </c>
-      <c r="F71" s="10">
+      <c r="F71">
         <v>9165424431</v>
       </c>
-      <c r="G71" s="9" t="s">
+      <c r="G71" t="s">
         <v>237</v>
       </c>
-      <c r="H71" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="4">
+      <c r="H71" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72">
         <v>46266.796076388891</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" t="s">
         <v>241</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" t="s">
         <v>242</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="D72" t="s">
         <v>243</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" t="s">
         <v>244</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72">
         <v>8109195869</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="G72" t="s">
         <v>241</v>
       </c>
-      <c r="H72" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="8">
+      <c r="H72" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73">
         <v>46266.811249999999</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" t="s">
         <v>245</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" t="s">
         <v>246</v>
       </c>
-      <c r="D73" s="9" t="s">
+      <c r="D73" t="s">
         <v>247</v>
       </c>
-      <c r="E73" s="9" t="s">
+      <c r="E73" t="s">
         <v>248</v>
       </c>
-      <c r="F73" s="10">
+      <c r="F73">
         <v>7974275417</v>
       </c>
-      <c r="G73" s="9" t="s">
+      <c r="G73" t="s">
         <v>245</v>
       </c>
-      <c r="H73" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="28">
+      <c r="H73" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74">
         <v>46266.727777777778</v>
       </c>
-      <c r="B74" s="29" t="s">
+      <c r="B74" t="s">
         <v>249</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" t="s">
         <v>250</v>
       </c>
-      <c r="D74" s="29" t="s">
+      <c r="D74" t="s">
         <v>251</v>
       </c>
-      <c r="E74" s="29" t="s">
+      <c r="E74" t="s">
         <v>251</v>
       </c>
-      <c r="F74" s="30">
+      <c r="F74">
         <v>9205383081</v>
       </c>
-      <c r="G74" s="29" t="s">
+      <c r="G74" t="s">
         <v>249</v>
       </c>
-      <c r="H74" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="16">
+      <c r="H74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75">
         <v>46266.727777777778</v>
       </c>
-      <c r="B75" s="17" t="s">
+      <c r="B75" t="s">
         <v>75</v>
       </c>
-      <c r="C75" s="31" t="s">
+      <c r="C75" t="s">
         <v>252</v>
       </c>
-      <c r="D75" s="17" t="s">
+      <c r="D75" t="s">
         <v>253</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E75" t="s">
         <v>254</v>
       </c>
-      <c r="F75" s="18" t="s">
+      <c r="F75" t="s">
         <v>255</v>
       </c>
-      <c r="G75" s="17" t="s">
+      <c r="G75" t="s">
         <v>75</v>
       </c>
-      <c r="H75" s="19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H75" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>256</v>
+      </c>
       <c r="B76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C76" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E76" t="s">
         <v>254</v>
@@ -3925,38 +3533,50 @@
         <v>9827222070</v>
       </c>
       <c r="G76" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="H76" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>256</v>
+      </c>
       <c r="B77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D77" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E77" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F77">
         <v>9779541247</v>
       </c>
       <c r="G77" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+      <c r="H77" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>256</v>
+      </c>
       <c r="B78" t="s">
         <v>170</v>
       </c>
       <c r="C78" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D78" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E78" t="s">
         <v>25</v>
@@ -3967,64 +3587,97 @@
       <c r="G78" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H78" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>256</v>
+      </c>
       <c r="B79" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C79" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D79" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E79" t="s">
         <v>25</v>
       </c>
+      <c r="F79" t="s">
+        <v>256</v>
+      </c>
       <c r="G79" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+      <c r="H79" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>256</v>
+      </c>
       <c r="B80" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C80" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D80" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E80" t="s">
         <v>16</v>
       </c>
+      <c r="F80" t="s">
+        <v>256</v>
+      </c>
       <c r="G80" t="s">
+        <v>269</v>
+      </c>
+      <c r="H80" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>256</v>
+      </c>
+      <c r="B81" t="s">
+        <v>272</v>
+      </c>
+      <c r="C81" t="s">
+        <v>273</v>
+      </c>
+      <c r="D81" t="s">
         <v>268</v>
-      </c>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
-        <v>271</v>
-      </c>
-      <c r="C81" t="s">
-        <v>272</v>
-      </c>
-      <c r="D81" t="s">
-        <v>267</v>
       </c>
       <c r="E81" t="s">
         <v>195</v>
       </c>
+      <c r="F81" t="s">
+        <v>256</v>
+      </c>
       <c r="G81" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+      <c r="H81" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>256</v>
+      </c>
       <c r="B82" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C82" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D82" t="s">
         <v>235</v>
@@ -4032,16 +3685,25 @@
       <c r="E82" t="s">
         <v>254</v>
       </c>
+      <c r="F82" t="s">
+        <v>256</v>
+      </c>
       <c r="G82" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="H82" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>256</v>
+      </c>
       <c r="B83" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C83" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D83" t="s">
         <v>235</v>
@@ -4049,16 +3711,25 @@
       <c r="E83" t="s">
         <v>254</v>
       </c>
+      <c r="F83" t="s">
+        <v>256</v>
+      </c>
       <c r="G83" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+      <c r="H83" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>256</v>
+      </c>
       <c r="B84" t="s">
         <v>245</v>
       </c>
       <c r="C84" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D84" t="s">
         <v>235</v>
@@ -4066,16 +3737,25 @@
       <c r="E84" t="s">
         <v>254</v>
       </c>
+      <c r="F84" t="s">
+        <v>256</v>
+      </c>
       <c r="G84" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H84" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>256</v>
+      </c>
       <c r="B85" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C85" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D85" t="s">
         <v>235</v>
@@ -4083,33 +3763,51 @@
       <c r="E85" t="s">
         <v>254</v>
       </c>
+      <c r="F85" t="s">
+        <v>256</v>
+      </c>
       <c r="G85" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="H85" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>256</v>
+      </c>
       <c r="B86" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C86" t="s">
         <v>226</v>
       </c>
       <c r="D86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E86" t="s">
         <v>254</v>
       </c>
+      <c r="F86" t="s">
+        <v>256</v>
+      </c>
       <c r="G86" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+      <c r="H86" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>256</v>
+      </c>
       <c r="B87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C87" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D87" t="s">
         <v>235</v>
@@ -4117,16 +3815,25 @@
       <c r="E87" t="s">
         <v>254</v>
       </c>
+      <c r="F87" t="s">
+        <v>256</v>
+      </c>
       <c r="G87" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+      <c r="H87" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>256</v>
+      </c>
       <c r="B88" t="s">
         <v>233</v>
       </c>
       <c r="C88" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D88" t="s">
         <v>235</v>
@@ -4134,19 +3841,28 @@
       <c r="E88" t="s">
         <v>254</v>
       </c>
+      <c r="F88" t="s">
+        <v>256</v>
+      </c>
       <c r="G88" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H88" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>256</v>
+      </c>
       <c r="B89" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C89" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D89" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E89" t="s">
         <v>25</v>
@@ -4155,15 +3871,21 @@
         <v>9826485375</v>
       </c>
       <c r="G89" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="H89" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>256</v>
+      </c>
       <c r="B90" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C90" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D90" t="s">
         <v>185</v>
@@ -4171,16 +3893,25 @@
       <c r="E90" t="s">
         <v>166</v>
       </c>
+      <c r="F90" t="s">
+        <v>256</v>
+      </c>
       <c r="G90" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+      <c r="H90" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>256</v>
+      </c>
       <c r="B91" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C91" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D91" t="s">
         <v>235</v>
@@ -4188,33 +3919,51 @@
       <c r="E91" t="s">
         <v>254</v>
       </c>
+      <c r="F91" t="s">
+        <v>256</v>
+      </c>
       <c r="G91" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+      <c r="H91" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>256</v>
+      </c>
       <c r="B92" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C92" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D92" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E92" t="s">
         <v>236</v>
       </c>
+      <c r="F92" t="s">
+        <v>256</v>
+      </c>
       <c r="G92" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="H92" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>256</v>
+      </c>
       <c r="B93" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C93" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D93" t="s">
         <v>235</v>
@@ -4222,16 +3971,25 @@
       <c r="E93" t="s">
         <v>35</v>
       </c>
+      <c r="F93" t="s">
+        <v>256</v>
+      </c>
       <c r="G93" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+      <c r="H93" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>256</v>
+      </c>
       <c r="B94" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C94" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D94" t="s">
         <v>235</v>
@@ -4239,16 +3997,25 @@
       <c r="E94" t="s">
         <v>39</v>
       </c>
+      <c r="F94" t="s">
+        <v>256</v>
+      </c>
       <c r="G94" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+      <c r="H94" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>256</v>
+      </c>
       <c r="B95" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C95" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D95" t="s">
         <v>235</v>
@@ -4256,16 +4023,25 @@
       <c r="E95" t="s">
         <v>39</v>
       </c>
+      <c r="F95" t="s">
+        <v>256</v>
+      </c>
       <c r="G95" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+      <c r="H95" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>256</v>
+      </c>
       <c r="B96" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C96" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D96" t="s">
         <v>235</v>
@@ -4273,16 +4049,25 @@
       <c r="E96" t="s">
         <v>74</v>
       </c>
+      <c r="F96" t="s">
+        <v>256</v>
+      </c>
       <c r="G96" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="H96" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>256</v>
+      </c>
       <c r="B97" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C97" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D97" t="s">
         <v>235</v>
@@ -4290,16 +4075,25 @@
       <c r="E97" t="s">
         <v>39</v>
       </c>
+      <c r="F97" t="s">
+        <v>256</v>
+      </c>
       <c r="G97" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+      <c r="H97" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>256</v>
+      </c>
       <c r="B98" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C98" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D98" t="s">
         <v>235</v>
@@ -4307,16 +4101,25 @@
       <c r="E98" t="s">
         <v>35</v>
       </c>
+      <c r="F98" t="s">
+        <v>256</v>
+      </c>
       <c r="G98" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+      <c r="H98" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>256</v>
+      </c>
       <c r="B99" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C99" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D99" t="s">
         <v>235</v>
@@ -4324,16 +4127,25 @@
       <c r="E99" t="s">
         <v>39</v>
       </c>
+      <c r="F99" t="s">
+        <v>256</v>
+      </c>
       <c r="G99" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+      <c r="H99" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>256</v>
+      </c>
       <c r="B100" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C100" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D100" t="s">
         <v>235</v>
@@ -4341,33 +4153,51 @@
       <c r="E100" t="s">
         <v>39</v>
       </c>
+      <c r="F100" t="s">
+        <v>256</v>
+      </c>
       <c r="G100" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="H100" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>256</v>
+      </c>
       <c r="B101" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C101" t="s">
+        <v>312</v>
+      </c>
+      <c r="D101" t="s">
+        <v>313</v>
+      </c>
+      <c r="E101" t="s">
+        <v>314</v>
+      </c>
+      <c r="F101" t="s">
+        <v>256</v>
+      </c>
+      <c r="G101" t="s">
         <v>311</v>
       </c>
-      <c r="D101" t="s">
-        <v>312</v>
-      </c>
-      <c r="E101" t="s">
-        <v>313</v>
-      </c>
-      <c r="G101" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H101" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>256</v>
+      </c>
       <c r="B102" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C102" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D102" t="s">
         <v>235</v>
@@ -4375,16 +4205,25 @@
       <c r="E102" t="s">
         <v>39</v>
       </c>
+      <c r="F102" t="s">
+        <v>256</v>
+      </c>
       <c r="G102" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+      <c r="H102" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>256</v>
+      </c>
       <c r="B103" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C103" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D103" t="s">
         <v>235</v>
@@ -4392,33 +4231,51 @@
       <c r="E103" t="s">
         <v>166</v>
       </c>
+      <c r="F103" t="s">
+        <v>256</v>
+      </c>
       <c r="G103" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+      <c r="H103" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>256</v>
+      </c>
       <c r="B104" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C104" t="s">
+        <v>320</v>
+      </c>
+      <c r="D104" t="s">
+        <v>321</v>
+      </c>
+      <c r="E104" t="s">
+        <v>322</v>
+      </c>
+      <c r="F104" t="s">
+        <v>256</v>
+      </c>
+      <c r="G104" t="s">
         <v>319</v>
       </c>
-      <c r="D104" t="s">
-        <v>320</v>
-      </c>
-      <c r="E104" t="s">
-        <v>321</v>
-      </c>
-      <c r="G104" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H104" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>256</v>
+      </c>
       <c r="B105" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C105" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D105" t="s">
         <v>73</v>
@@ -4430,15 +4287,21 @@
         <v>7057726152</v>
       </c>
       <c r="G105" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="H105" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>256</v>
+      </c>
       <c r="B106" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C106" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D106" t="s">
         <v>235</v>
@@ -4446,16 +4309,25 @@
       <c r="E106" t="s">
         <v>39</v>
       </c>
+      <c r="F106" t="s">
+        <v>256</v>
+      </c>
       <c r="G106" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+      <c r="H106" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>256</v>
+      </c>
       <c r="B107" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C107" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D107" t="s">
         <v>235</v>
@@ -4463,16 +4335,25 @@
       <c r="E107" t="s">
         <v>254</v>
       </c>
+      <c r="F107" t="s">
+        <v>256</v>
+      </c>
       <c r="G107" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+      <c r="H107" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>256</v>
+      </c>
       <c r="B108" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C108" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D108" t="s">
         <v>235</v>
@@ -4480,64 +4361,103 @@
       <c r="E108" t="s">
         <v>254</v>
       </c>
+      <c r="F108" t="s">
+        <v>256</v>
+      </c>
       <c r="G108" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="H108" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>256</v>
+      </c>
       <c r="B109" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C109" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D109" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E109" t="s">
         <v>236</v>
       </c>
+      <c r="F109" t="s">
+        <v>256</v>
+      </c>
       <c r="G109" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+      <c r="H109" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>256</v>
+      </c>
+      <c r="B110" t="s">
+        <v>256</v>
+      </c>
       <c r="C110" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D110" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E110" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F110">
         <v>9826516616</v>
       </c>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G110" t="s">
+        <v>256</v>
+      </c>
+      <c r="H110" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>256</v>
+      </c>
       <c r="B111" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C111" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D111" t="s">
         <v>178</v>
       </c>
       <c r="E111" t="s">
-        <v>335</v>
+        <v>336</v>
+      </c>
+      <c r="F111" t="s">
+        <v>256</v>
       </c>
       <c r="G111" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+      <c r="H111" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>256</v>
+      </c>
       <c r="B112" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C112" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D112" t="s">
         <v>73</v>
@@ -4545,16 +4465,25 @@
       <c r="E112" t="s">
         <v>236</v>
       </c>
+      <c r="F112" t="s">
+        <v>256</v>
+      </c>
       <c r="G112" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="H112" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>256</v>
+      </c>
       <c r="B113" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C113" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D113" t="s">
         <v>235</v>
@@ -4562,50 +4491,77 @@
       <c r="E113" t="s">
         <v>25</v>
       </c>
+      <c r="F113" t="s">
+        <v>256</v>
+      </c>
       <c r="G113" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+      <c r="H113" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>256</v>
+      </c>
       <c r="B114" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C114" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D114" t="s">
         <v>235</v>
       </c>
       <c r="E114" t="s">
-        <v>335</v>
+        <v>336</v>
+      </c>
+      <c r="F114" t="s">
+        <v>256</v>
       </c>
       <c r="G114" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+      <c r="H114" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>256</v>
+      </c>
       <c r="B115" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C115" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D115" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E115" t="s">
         <v>254</v>
       </c>
+      <c r="F115" t="s">
+        <v>256</v>
+      </c>
       <c r="G115" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+      <c r="H115" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>256</v>
+      </c>
       <c r="B116" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C116" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D116" t="s">
         <v>235</v>
@@ -4613,33 +4569,51 @@
       <c r="E116" t="s">
         <v>254</v>
       </c>
+      <c r="F116" t="s">
+        <v>256</v>
+      </c>
       <c r="G116" t="s">
+        <v>348</v>
+      </c>
+      <c r="H116" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>256</v>
+      </c>
+      <c r="B117" t="s">
+        <v>350</v>
+      </c>
+      <c r="C117" t="s">
+        <v>351</v>
+      </c>
+      <c r="D117" t="s">
         <v>347</v>
-      </c>
-    </row>
-    <row r="117" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B117" t="s">
-        <v>349</v>
-      </c>
-      <c r="C117" t="s">
-        <v>350</v>
-      </c>
-      <c r="D117" t="s">
-        <v>346</v>
       </c>
       <c r="E117" t="s">
         <v>254</v>
       </c>
+      <c r="F117" t="s">
+        <v>256</v>
+      </c>
       <c r="G117" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="H117" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>256</v>
+      </c>
       <c r="B118" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C118" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D118" t="s">
         <v>235</v>
@@ -4647,16 +4621,25 @@
       <c r="E118" t="s">
         <v>166</v>
       </c>
+      <c r="F118" t="s">
+        <v>256</v>
+      </c>
       <c r="G118" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+      <c r="H118" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>256</v>
+      </c>
       <c r="B119" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C119" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D119" t="s">
         <v>235</v>
@@ -4664,33 +4647,51 @@
       <c r="E119" t="s">
         <v>166</v>
       </c>
+      <c r="F119" t="s">
+        <v>256</v>
+      </c>
       <c r="G119" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+      <c r="H119" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>256</v>
+      </c>
       <c r="B120" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C120" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D120" t="s">
         <v>235</v>
       </c>
       <c r="E120" t="s">
-        <v>335</v>
+        <v>336</v>
+      </c>
+      <c r="F120" t="s">
+        <v>256</v>
       </c>
       <c r="G120" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+      <c r="H120" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>256</v>
+      </c>
       <c r="B121" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C121" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D121" t="s">
         <v>235</v>
@@ -4698,16 +4699,25 @@
       <c r="E121" t="s">
         <v>254</v>
       </c>
+      <c r="F121" t="s">
+        <v>256</v>
+      </c>
       <c r="G121" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+      <c r="H121" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>256</v>
+      </c>
       <c r="B122" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C122" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D122" t="s">
         <v>235</v>
@@ -4715,16 +4725,25 @@
       <c r="E122" t="s">
         <v>254</v>
       </c>
+      <c r="F122" t="s">
+        <v>256</v>
+      </c>
       <c r="G122" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+      <c r="H122" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>256</v>
+      </c>
       <c r="B123" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C123" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D123" t="s">
         <v>235</v>
@@ -4732,50 +4751,77 @@
       <c r="E123" t="s">
         <v>254</v>
       </c>
+      <c r="F123" t="s">
+        <v>256</v>
+      </c>
       <c r="G123" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+      <c r="H123" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>256</v>
+      </c>
       <c r="B124" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C124" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D124" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E124" t="s">
         <v>254</v>
       </c>
+      <c r="F124" t="s">
+        <v>256</v>
+      </c>
       <c r="G124" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="125" spans="2:7" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+      <c r="H124" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>256</v>
+      </c>
       <c r="B125" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C125" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D125" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E125" t="s">
         <v>254</v>
       </c>
+      <c r="F125" t="s">
+        <v>256</v>
+      </c>
       <c r="G125" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="126" spans="2:7" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+      <c r="H125" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>256</v>
+      </c>
       <c r="B126" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C126" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D126" t="s">
         <v>235</v>
@@ -4783,16 +4829,25 @@
       <c r="E126" t="s">
         <v>254</v>
       </c>
+      <c r="F126" t="s">
+        <v>256</v>
+      </c>
       <c r="G126" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="127" spans="2:7" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+      <c r="H126" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>256</v>
+      </c>
       <c r="B127" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C127" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D127" t="s">
         <v>73</v>
@@ -4800,16 +4855,25 @@
       <c r="E127" t="s">
         <v>236</v>
       </c>
+      <c r="F127" t="s">
+        <v>256</v>
+      </c>
       <c r="G127" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="128" spans="2:7" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+      <c r="H127" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>256</v>
+      </c>
       <c r="B128" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C128" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D128" t="s">
         <v>73</v>
@@ -4817,16 +4881,25 @@
       <c r="E128" t="s">
         <v>236</v>
       </c>
+      <c r="F128" t="s">
+        <v>256</v>
+      </c>
       <c r="G128" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="129" spans="2:7" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="H128" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>256</v>
+      </c>
       <c r="B129" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C129" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D129" t="s">
         <v>73</v>
@@ -4834,16 +4907,25 @@
       <c r="E129" t="s">
         <v>236</v>
       </c>
+      <c r="F129" t="s">
+        <v>256</v>
+      </c>
       <c r="G129" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="130" spans="2:7" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+      <c r="H129" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>256</v>
+      </c>
       <c r="B130" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C130" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D130" t="s">
         <v>51</v>
@@ -4851,16 +4933,25 @@
       <c r="E130" t="s">
         <v>236</v>
       </c>
+      <c r="F130" t="s">
+        <v>256</v>
+      </c>
       <c r="G130" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="H130" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>256</v>
+      </c>
       <c r="B131" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C131" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D131" t="s">
         <v>51</v>
@@ -4868,33 +4959,51 @@
       <c r="E131" t="s">
         <v>236</v>
       </c>
+      <c r="F131" t="s">
+        <v>256</v>
+      </c>
       <c r="G131" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="132" spans="2:7" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="H131" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>256</v>
+      </c>
       <c r="B132" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C132" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D132" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E132" t="s">
         <v>254</v>
       </c>
+      <c r="F132" t="s">
+        <v>256</v>
+      </c>
       <c r="G132" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="133" spans="2:7" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="H132" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>256</v>
+      </c>
       <c r="B133" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C133" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D133" t="s">
         <v>235</v>
@@ -4902,16 +5011,25 @@
       <c r="E133" t="s">
         <v>254</v>
       </c>
+      <c r="F133" t="s">
+        <v>256</v>
+      </c>
       <c r="G133" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="134" spans="2:7" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+      <c r="H133" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>256</v>
+      </c>
       <c r="B134" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C134" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D134" t="s">
         <v>235</v>
@@ -4919,16 +5037,25 @@
       <c r="E134" t="s">
         <v>254</v>
       </c>
+      <c r="F134" t="s">
+        <v>256</v>
+      </c>
       <c r="G134" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="135" spans="2:7" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+      <c r="H134" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>256</v>
+      </c>
       <c r="B135" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C135" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D135" t="s">
         <v>73</v>
@@ -4936,11 +5063,84 @@
       <c r="E135" t="s">
         <v>74</v>
       </c>
+      <c r="F135" t="s">
+        <v>256</v>
+      </c>
       <c r="G135" t="s">
-        <v>338</v>
+        <v>339</v>
+      </c>
+      <c r="H135" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>319</v>
+      </c>
+      <c r="C136" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
+        <v>274</v>
+      </c>
+      <c r="C137" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>233</v>
+      </c>
+      <c r="C138" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>283</v>
+      </c>
+      <c r="C139" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>245</v>
+      </c>
+      <c r="C140" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>279</v>
+      </c>
+      <c r="C141" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>276</v>
+      </c>
+      <c r="C142" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>386</v>
+      </c>
+      <c r="C143" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:H143" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/public/assets/ICF Workshop.xlsx
+++ b/public/assets/ICF Workshop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\amaltas-university-latest\amaltas-university\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C27B8A-5DF4-4618-9428-78D2A0E8186B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7736CF14-1FF1-42B5-A555-3F84898CFBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="390">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1184,6 +1184,12 @@
   </si>
   <si>
     <t>Dr. Vijay Bairagi</t>
+  </si>
+  <si>
+    <t>Dr. Abhay Gupta</t>
+  </si>
+  <si>
+    <t>abhay@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1560,10 +1566,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H143"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H144"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="31.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1589,7 +1599,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>46252.694108796299</v>
       </c>
@@ -1615,7 +1625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>46255.475023148138</v>
       </c>
@@ -1641,7 +1651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>46255.476666666669</v>
       </c>
@@ -1667,7 +1677,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>46255.505543981482</v>
       </c>
@@ -1693,7 +1703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>46255.507199074083</v>
       </c>
@@ -1719,7 +1729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>46255.510648148149</v>
       </c>
@@ -1745,7 +1755,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>46255.510937500003</v>
       </c>
@@ -1771,7 +1781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>46255.510949074072</v>
       </c>
@@ -1797,7 +1807,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>46255.511736111112</v>
       </c>
@@ -1823,7 +1833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>46255.512418981481</v>
       </c>
@@ -1849,7 +1859,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>46255.512916666667</v>
       </c>
@@ -1875,7 +1885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>46255.514189814807</v>
       </c>
@@ -1901,7 +1911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>46255.515092592592</v>
       </c>
@@ -1927,7 +1937,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>46255.545069444437</v>
       </c>
@@ -1953,7 +1963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>46255.556342592587</v>
       </c>
@@ -1979,7 +1989,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>46255.569016203714</v>
       </c>
@@ -2005,7 +2015,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>46255.583124999997</v>
       </c>
@@ -2031,7 +2041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>46255.601620370369</v>
       </c>
@@ -2057,7 +2067,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>46255.715567129628</v>
       </c>
@@ -2083,7 +2093,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>46255.716550925928</v>
       </c>
@@ -2109,7 +2119,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>46255.758125</v>
       </c>
@@ -2135,7 +2145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>46256.371238425927</v>
       </c>
@@ -2161,7 +2171,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>46256.462129629632</v>
       </c>
@@ -2187,7 +2197,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>46258.460543981477</v>
       </c>
@@ -2213,7 +2223,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>46258.629189814812</v>
       </c>
@@ -2239,7 +2249,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>46258.635474537034</v>
       </c>
@@ -2265,7 +2275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>46258.657175925917</v>
       </c>
@@ -2291,7 +2301,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>46258.657407407409</v>
       </c>
@@ -2317,7 +2327,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>46258.657812500001</v>
       </c>
@@ -2343,7 +2353,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>46258.666689814818</v>
       </c>
@@ -2369,7 +2379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>46258.680208333331</v>
       </c>
@@ -2395,7 +2405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>46260.799618055556</v>
       </c>
@@ -2421,7 +2431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>46260.972731481481</v>
       </c>
@@ -2447,7 +2457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>46261.376689814817</v>
       </c>
@@ -2473,7 +2483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>46261.445763888893</v>
       </c>
@@ -2499,7 +2509,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>46263.532326388893</v>
       </c>
@@ -2525,7 +2535,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>46263.532361111109</v>
       </c>
@@ -2551,7 +2561,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>46263.53329861111</v>
       </c>
@@ -2577,7 +2587,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>46263.534525462957</v>
       </c>
@@ -2603,7 +2613,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>46263.535405092603</v>
       </c>
@@ -2629,7 +2639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>46263.53564814815</v>
       </c>
@@ -2655,7 +2665,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>46263.535844907397</v>
       </c>
@@ -2681,7 +2691,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>46263.536226851851</v>
       </c>
@@ -2707,7 +2717,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>46263.538194444453</v>
       </c>
@@ -2733,7 +2743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>46263.539305555547</v>
       </c>
@@ -2759,7 +2769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46263.539988425917</v>
       </c>
@@ -2785,7 +2795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>46263.541504629633</v>
       </c>
@@ -2811,7 +2821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>46263.541817129633</v>
       </c>
@@ -2837,7 +2847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>46263.544178240743</v>
       </c>
@@ -2863,7 +2873,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>46263.545567129629</v>
       </c>
@@ -2889,7 +2899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>46263.548356481479</v>
       </c>
@@ -2915,7 +2925,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>46263.550671296303</v>
       </c>
@@ -2941,7 +2951,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>46263.558761574073</v>
       </c>
@@ -2967,7 +2977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>46263.560706018521</v>
       </c>
@@ -2993,7 +3003,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>46263.564583333333</v>
       </c>
@@ -3019,7 +3029,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>46263.573020833333</v>
       </c>
@@ -3045,7 +3055,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>46263.576574074083</v>
       </c>
@@ -3071,7 +3081,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>46263.578310185178</v>
       </c>
@@ -3097,7 +3107,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>46263.593414351853</v>
       </c>
@@ -3123,7 +3133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>46263.749513888892</v>
       </c>
@@ -3149,7 +3159,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>46265.339282407411</v>
       </c>
@@ -3175,7 +3185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>46265.34171296296</v>
       </c>
@@ -3201,7 +3211,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>46265.612719907411</v>
       </c>
@@ -3227,7 +3237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>46266.355821759258</v>
       </c>
@@ -3253,7 +3263,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>46266.376076388893</v>
       </c>
@@ -3279,7 +3289,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>46266.376111111109</v>
       </c>
@@ -3305,7 +3315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>46266.515208333331</v>
       </c>
@@ -3331,7 +3341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>46266.723414351851</v>
       </c>
@@ -3357,7 +3367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>46266.726030092592</v>
       </c>
@@ -3383,7 +3393,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>46266.784849537027</v>
       </c>
@@ -3409,7 +3419,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>46266.796076388891</v>
       </c>
@@ -3435,7 +3445,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>46266.811249999999</v>
       </c>
@@ -3461,7 +3471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>46266.727777777778</v>
       </c>
@@ -3487,7 +3497,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>46266.727777777778</v>
       </c>
@@ -3513,7 +3523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>256</v>
       </c>
@@ -3539,7 +3549,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>256</v>
       </c>
@@ -3565,7 +3575,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>256</v>
       </c>
@@ -3591,7 +3601,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>256</v>
       </c>
@@ -3617,7 +3627,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>256</v>
       </c>
@@ -3643,7 +3653,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>256</v>
       </c>
@@ -3669,7 +3679,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>256</v>
       </c>
@@ -3695,7 +3705,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>256</v>
       </c>
@@ -3721,7 +3731,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>256</v>
       </c>
@@ -3747,7 +3757,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>256</v>
       </c>
@@ -3773,7 +3783,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>256</v>
       </c>
@@ -3799,7 +3809,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>256</v>
       </c>
@@ -3825,7 +3835,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>256</v>
       </c>
@@ -3851,7 +3861,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>256</v>
       </c>
@@ -3877,7 +3887,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>256</v>
       </c>
@@ -3903,7 +3913,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>256</v>
       </c>
@@ -3929,7 +3939,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>256</v>
       </c>
@@ -3955,7 +3965,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>256</v>
       </c>
@@ -3981,7 +3991,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>256</v>
       </c>
@@ -4007,7 +4017,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>256</v>
       </c>
@@ -4033,7 +4043,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>256</v>
       </c>
@@ -4059,7 +4069,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>256</v>
       </c>
@@ -4085,7 +4095,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>256</v>
       </c>
@@ -4111,7 +4121,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>256</v>
       </c>
@@ -4137,7 +4147,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>256</v>
       </c>
@@ -4163,7 +4173,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>256</v>
       </c>
@@ -4189,7 +4199,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>256</v>
       </c>
@@ -4215,7 +4225,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>256</v>
       </c>
@@ -4241,7 +4251,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>256</v>
       </c>
@@ -4267,7 +4277,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>256</v>
       </c>
@@ -4293,7 +4303,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>256</v>
       </c>
@@ -4319,7 +4329,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>256</v>
       </c>
@@ -4345,7 +4355,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>256</v>
       </c>
@@ -4371,7 +4381,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>256</v>
       </c>
@@ -4397,7 +4407,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>256</v>
       </c>
@@ -4423,7 +4433,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>256</v>
       </c>
@@ -4449,7 +4459,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>256</v>
       </c>
@@ -4475,7 +4485,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>256</v>
       </c>
@@ -4501,7 +4511,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>256</v>
       </c>
@@ -4527,7 +4537,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>256</v>
       </c>
@@ -4553,7 +4563,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>256</v>
       </c>
@@ -4579,7 +4589,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>256</v>
       </c>
@@ -4605,7 +4615,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>256</v>
       </c>
@@ -4631,7 +4641,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>256</v>
       </c>
@@ -4657,7 +4667,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>256</v>
       </c>
@@ -4683,7 +4693,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>256</v>
       </c>
@@ -4709,7 +4719,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>256</v>
       </c>
@@ -4735,7 +4745,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>256</v>
       </c>
@@ -4761,7 +4771,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>256</v>
       </c>
@@ -4787,7 +4797,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>256</v>
       </c>
@@ -4813,7 +4823,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>256</v>
       </c>
@@ -4839,7 +4849,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>256</v>
       </c>
@@ -4865,7 +4875,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>256</v>
       </c>
@@ -4891,7 +4901,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>256</v>
       </c>
@@ -4917,7 +4927,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>256</v>
       </c>
@@ -4943,7 +4953,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>256</v>
       </c>
@@ -4969,7 +4979,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>256</v>
       </c>
@@ -4995,7 +5005,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>256</v>
       </c>
@@ -5021,7 +5031,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>256</v>
       </c>
@@ -5047,7 +5057,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>256</v>
       </c>
@@ -5073,7 +5083,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
         <v>319</v>
       </c>
@@ -5081,7 +5091,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
         <v>274</v>
       </c>
@@ -5089,7 +5099,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
         <v>233</v>
       </c>
@@ -5097,7 +5107,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
         <v>283</v>
       </c>
@@ -5105,7 +5115,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
         <v>245</v>
       </c>
@@ -5113,7 +5123,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
         <v>279</v>
       </c>
@@ -5121,7 +5131,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
         <v>276</v>
       </c>
@@ -5129,12 +5139,20 @@
         <v>277</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
         <v>386</v>
       </c>
       <c r="C143" t="s">
         <v>387</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>389</v>
+      </c>
+      <c r="C144" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>
